--- a/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 19,23</t>
+          <t>8,46; 18,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 14,17</t>
+          <t>3,78; 14,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 17,21</t>
+          <t>6,08; 17,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 7,72</t>
+          <t>-8,72; 7,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 44,68</t>
+          <t>17,57; 43,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 25,54</t>
+          <t>6,45; 25,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 36,02</t>
+          <t>11,01; 35,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 21,32</t>
+          <t>-19,66; 19,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,36; 21,61</t>
+          <t>12,35; 21,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 20,98</t>
+          <t>12,05; 21,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 19,88</t>
+          <t>10,1; 19,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 30,06</t>
+          <t>6,16; 29,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 50,46</t>
+          <t>25,82; 49,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,8; 42,78</t>
+          <t>22,37; 43,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,29; 43,17</t>
+          <t>19,65; 41,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 201,17</t>
+          <t>16,5; 168,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 20,38</t>
+          <t>9,73; 20,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 22,63</t>
+          <t>12,05; 22,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,43</t>
+          <t>6,16; 16,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 40,97</t>
+          <t>0,17; 43,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,47; 49,08</t>
+          <t>20,82; 50,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,9; 49,21</t>
+          <t>23,39; 49,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 37,42</t>
+          <t>12,25; 36,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 132,82</t>
+          <t>0,6; 150,2</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 21,51</t>
+          <t>12,78; 21,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 15,93</t>
+          <t>6,82; 15,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 12,57</t>
+          <t>3,57; 12,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 8,99</t>
+          <t>-3,6; 9,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,7; 54,02</t>
+          <t>29,06; 53,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 29,17</t>
+          <t>11,61; 29,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 25,33</t>
+          <t>6,68; 24,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 30,33</t>
+          <t>-10,09; 32,33</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,43</t>
+          <t>13,69; 18,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,1</t>
+          <t>11,39; 16,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,95</t>
+          <t>9,39; 13,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 22,02</t>
+          <t>4,72; 23,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,96; 42,9</t>
+          <t>29,99; 43,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,88; 30,53</t>
+          <t>20,51; 30,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 28,53</t>
+          <t>18,25; 29,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,84; 78,75</t>
+          <t>14,02; 81,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>6,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 18,78</t>
+          <t>8,92; 19,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,09</t>
+          <t>3,81; 13,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 17,05</t>
+          <t>6,08; 17,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 7,2</t>
+          <t>1,61; 11,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 43,59</t>
+          <t>18,2; 44,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 25,03</t>
+          <t>6,12; 24,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 35,76</t>
+          <t>11,35; 35,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 19,95</t>
+          <t>4,29; 33,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,25</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 21,41</t>
+          <t>12,44; 21,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,05; 21,09</t>
+          <t>12,28; 20,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 19,24</t>
+          <t>10,41; 19,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 29,02</t>
+          <t>4,49; 12,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,82; 49,86</t>
+          <t>26,44; 50,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,37; 43,07</t>
+          <t>22,24; 42,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 41,9</t>
+          <t>20,15; 40,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 168,95</t>
+          <t>12,09; 40,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,71</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 20,7</t>
+          <t>9,86; 20,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 22,65</t>
+          <t>12,22; 22,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 16,31</t>
+          <t>6,17; 16,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 43,63</t>
+          <t>-1,03; 8,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,82; 50,12</t>
+          <t>21,28; 48,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,39; 49,56</t>
+          <t>23,63; 48,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 36,32</t>
+          <t>12,61; 38,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 150,2</t>
+          <t>-3,03; 30,27</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 21,34</t>
+          <t>12,78; 21,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 15,53</t>
+          <t>6,17; 15,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,38</t>
+          <t>3,84; 12,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,68</t>
+          <t>3,72; 11,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,06; 53,83</t>
+          <t>29,04; 54,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 29,31</t>
+          <t>10,56; 28,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 24,47</t>
+          <t>7,05; 25,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 32,33</t>
+          <t>11,55; 42,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,36</t>
+          <t>13,65; 18,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 16,26</t>
+          <t>11,34; 16,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,98</t>
+          <t>9,13; 13,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 23,1</t>
+          <t>4,73; 9,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,99; 43,08</t>
+          <t>29,81; 42,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,51; 30,79</t>
+          <t>20,6; 30,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,25; 29,04</t>
+          <t>17,98; 29,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,02; 81,34</t>
+          <t>13,9; 28,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
